--- a/screen.xlsx
+++ b/screen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7E5612-06A9-4022-BA47-B36B36E863B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BA3C69-5D4F-46A7-B3FD-4459D46A8300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="98">
   <si>
     <t>a</t>
   </si>
@@ -63,9 +63,6 @@
     <t>r</t>
   </si>
   <si>
-    <t>tooth</t>
-  </si>
-  <si>
     <t>360-импульсов на оборот</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>s</t>
   </si>
   <si>
-    <t>пуск или настройки</t>
-  </si>
-  <si>
     <t>360/(tooth-1)</t>
   </si>
   <si>
@@ -141,12 +135,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>Set</t>
-  </si>
-  <si>
-    <t>save</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
@@ -189,15 +177,6 @@
     <t>m1_M</t>
   </si>
   <si>
-    <t>max speed</t>
-  </si>
-  <si>
-    <t>тут тестирование может сделаю в будущем, так-то просто вобьем константу</t>
-  </si>
-  <si>
-    <t>40*50*36</t>
-  </si>
-  <si>
     <t>импульсов на оборот, для удг формула =передаточноеУДГ*передаточноеМ*числоимп_энк  далее делим на число зубов</t>
   </si>
   <si>
@@ -213,9 +192,6 @@
     <t>StDiEn</t>
   </si>
   <si>
-    <t>Step, Dir, En inverse</t>
-  </si>
-  <si>
     <t>RCP ждать или нет? 0 не ждать, 1 ждать еденицу, 2 ждать нолик (инверсия)</t>
   </si>
   <si>
@@ -240,9 +216,6 @@
     <t>Запущен</t>
   </si>
   <si>
-    <t>enter_ прерывает процесс</t>
-  </si>
-  <si>
     <t>S1</t>
   </si>
   <si>
@@ -280,6 +253,81 @@
   </si>
   <si>
     <t>подсветка экрана вкл</t>
+  </si>
+  <si>
+    <t>основной экран</t>
+  </si>
+  <si>
+    <t>дополнительный экран</t>
+  </si>
+  <si>
+    <t>настройки 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set </t>
+  </si>
+  <si>
+    <t>настройки</t>
+  </si>
+  <si>
+    <t>пуск/стоп</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>RCP reach contol point (дошел до уставки дискретный сигнал)</t>
+  </si>
+  <si>
+    <t>Sw1 концевики</t>
+  </si>
+  <si>
+    <t>Sw1_i инверсия концевика</t>
+  </si>
+  <si>
+    <t>M1 L/R вращение левое правое</t>
+  </si>
+  <si>
+    <t>Step, Dir, En inverse инверсия выходных сигналов</t>
+  </si>
+  <si>
+    <t>40*88(88 это число импульсов на обород моего двигателя)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test </t>
+  </si>
+  <si>
+    <t>провернет на оборот (указанное число импульсов) для m2 не критично всеравно по концевикам работает ставим 1000</t>
+  </si>
+  <si>
+    <t>max speed в импульсах в 0.1 секунд</t>
+  </si>
+  <si>
+    <t>тут тестирование может сделаю в будущем, так-то просто вобьем константу, эта скорость будет максимальной, например надо будет найти максимальную скорость от числа импульсов так чтобы шаги не пропускались (если шд) это и будет 100% на галвном экране</t>
+  </si>
+  <si>
+    <t>настройки 2</t>
+  </si>
+  <si>
+    <t>настройки 3</t>
+  </si>
+  <si>
+    <t>настройки 4</t>
+  </si>
+  <si>
+    <t>настройки 5</t>
+  </si>
+  <si>
+    <t>настройки 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">для перехода тут надо удерживать кнопку enter </t>
+  </si>
+  <si>
+    <t>если удерживать кнопку вверх то возврат без сохранения (во всех экранах настроек)</t>
+  </si>
+  <si>
+    <t>минус_ прерывает процесс</t>
   </si>
 </sst>
 </file>
@@ -497,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -511,13 +559,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -832,29 +882,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE51753-6362-42E1-858B-3262C08793D0}">
-  <dimension ref="B4:Z37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A4:Z37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="12" width="2.6640625" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="14" width="3.109375" customWidth="1"/>
-    <col min="15" max="15" width="3.21875" customWidth="1"/>
-    <col min="16" max="16" width="3" customWidth="1"/>
-    <col min="17" max="17" width="3.21875" customWidth="1"/>
-    <col min="18" max="18" width="3.109375" customWidth="1"/>
-    <col min="24" max="24" width="68.21875" customWidth="1"/>
-    <col min="26" max="26" width="60.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="12" width="2.7109375" customWidth="1"/>
+    <col min="13" max="13" width="3.42578125" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="3.28515625" customWidth="1"/>
+    <col min="18" max="18" width="3.140625" customWidth="1"/>
+    <col min="23" max="23" width="59.28515625" customWidth="1"/>
+    <col min="24" max="24" width="68.28515625" customWidth="1"/>
+    <col min="26" max="26" width="60.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="V4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>0</v>
       </c>
@@ -904,42 +957,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="X6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8" t="s">
@@ -961,19 +1017,20 @@
         <v>6</v>
       </c>
       <c r="V7" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
       <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
@@ -1017,27 +1074,21 @@
         <v>6</v>
       </c>
       <c r="V8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W8" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="Z8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="V9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>0</v>
       </c>
@@ -1087,18 +1138,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="8">
         <v>1</v>
@@ -1107,24 +1161,24 @@
         <v>5</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>4</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P11" s="8">
         <v>1</v>
@@ -1133,21 +1187,31 @@
         <v>5</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="V11" t="s">
+        <v>76</v>
+      </c>
+      <c r="W11" t="s">
+        <v>77</v>
+      </c>
+      <c r="X11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
       <c r="C12" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="11">
         <v>2</v>
@@ -1156,24 +1220,24 @@
         <v>5</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="L12" s="11">
         <v>1</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P12" s="11">
         <v>2</v>
@@ -1182,31 +1246,37 @@
         <v>5</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="W12" t="s">
+        <v>72</v>
+      </c>
+      <c r="X12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>75</v>
+      </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" s="8">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>3</v>
@@ -1219,51 +1289,55 @@
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M14" s="8">
         <v>1</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="R14" s="14">
+        <v>21</v>
+      </c>
+      <c r="R14" s="9">
         <v>2</v>
       </c>
-      <c r="S14" s="17" t="s">
-        <v>56</v>
+      <c r="S14" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="V14" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="W14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="X14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
       <c r="C15" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15" s="11">
         <v>2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>3</v>
@@ -1276,7 +1350,7 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L15" s="11">
         <v>1</v>
@@ -1288,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P15" s="11">
         <v>2</v>
@@ -1300,21 +1374,24 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="W15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="W16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>90</v>
+      </c>
       <c r="B17">
         <v>3</v>
       </c>
@@ -1328,26 +1405,26 @@
         <v>5</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>2</v>
@@ -1365,13 +1442,17 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="X17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
       <c r="C18" s="10" t="s">
         <v>7</v>
       </c>
@@ -1382,26 +1463,26 @@
         <v>5</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="11" t="s">
         <v>8</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>2</v>
@@ -1419,14 +1500,17 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="W18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:26" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>91</v>
+      </c>
       <c r="B20">
         <v>4</v>
       </c>
@@ -1437,59 +1521,60 @@
         <v>1</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="N20" s="8"/>
       <c r="O20" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="R20" s="14" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="V20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="W20" t="s">
-        <v>45</v>
-      </c>
-      <c r="X20" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="X20" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="Z20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17"/>
       <c r="C21" s="10" t="s">
         <v>7</v>
       </c>
@@ -1497,48 +1582,57 @@
         <v>2</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="N21" s="11"/>
       <c r="O21" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="R21" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="V21" t="s">
+        <v>86</v>
+      </c>
+      <c r="W21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>92</v>
+      </c>
       <c r="B23">
         <v>5</v>
       </c>
@@ -1549,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>7</v>
@@ -1558,45 +1652,46 @@
         <v>5</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M23" s="8"/>
-      <c r="N23" s="13"/>
+      <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="R23" s="14" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="V23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="W23" t="s">
-        <v>51</v>
-      </c>
-      <c r="X23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="X23" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
       <c r="C24" s="10" t="s">
         <v>7</v>
       </c>
@@ -1604,7 +1699,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>7</v>
@@ -1613,48 +1708,58 @@
         <v>5</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M24" s="11"/>
-      <c r="N24" s="15"/>
+      <c r="N24" s="11"/>
       <c r="O24" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>4</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>4</v>
@@ -1664,31 +1769,32 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -1706,7 +1812,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="6"/>
     </row>
-    <row r="28" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>0</v>
       </c>
@@ -1756,101 +1862,105 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>94</v>
+      </c>
       <c r="B29">
         <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="6"/>
     </row>
-    <row r="31" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
-        <v>67</v>
+    <row r="31" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>5</v>
@@ -1867,10 +1977,10 @@
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>8</v>
@@ -1879,37 +1989,37 @@
         <v>5</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R32" s="9"/>
       <c r="V32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="18">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="14">
         <v>8</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G33" s="11">
         <v>1</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="15" t="s">
         <v>5</v>
       </c>
       <c r="I33" s="5">
@@ -1917,7 +2027,7 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L33" s="11">
         <v>2</v>
@@ -1931,51 +2041,61 @@
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R33" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V33" t="s">
+        <v>60</v>
+      </c>
+      <c r="W33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V34" t="s">
+        <v>62</v>
+      </c>
+      <c r="W34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V35" t="s">
+        <v>64</v>
+      </c>
+      <c r="W35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V36" t="s">
+        <v>66</v>
+      </c>
+      <c r="W36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W37" t="s">
         <v>69</v>
       </c>
-      <c r="W33" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V34" t="s">
-        <v>71</v>
-      </c>
-      <c r="W34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V35" t="s">
-        <v>73</v>
-      </c>
-      <c r="W35" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V36" t="s">
-        <v>75</v>
-      </c>
-      <c r="W36" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V37" t="s">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s">
-        <v>78</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A23:A24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BA3C69-5D4F-46A7-B3FD-4459D46A8300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B907F61-34F1-417E-88C6-66164D9D94AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="101">
   <si>
     <t>a</t>
   </si>
@@ -258,9 +258,6 @@
     <t>основной экран</t>
   </si>
   <si>
-    <t>дополнительный экран</t>
-  </si>
-  <si>
     <t>настройки 1</t>
   </si>
   <si>
@@ -328,6 +325,18 @@
   </si>
   <si>
     <t>минус_ прерывает процесс</t>
+  </si>
+  <si>
+    <t>настройки 0</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>RCP 11</t>
+  </si>
+  <si>
+    <t>влево вправо перемещение курсора, интер выбор и потом вверх вниз увеличить или уменьшить, ентер ввод вверх назад (выйти из энтера, курсор на 0)</t>
   </si>
 </sst>
 </file>
@@ -882,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE51753-6362-42E1-858B-3262C08793D0}">
-  <dimension ref="A4:Z37"/>
+  <dimension ref="A4:Z38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -894,6 +903,7 @@
     <col min="16" max="16" width="3.7109375" customWidth="1"/>
     <col min="17" max="17" width="3.28515625" customWidth="1"/>
     <col min="18" max="18" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="53.5703125" customWidth="1"/>
     <col min="23" max="23" width="59.28515625" customWidth="1"/>
     <col min="24" max="24" width="68.28515625" customWidth="1"/>
     <col min="26" max="26" width="60.28515625" customWidth="1"/>
@@ -965,7 +975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>73</v>
       </c>
@@ -998,26 +1008,23 @@
         <v>25</v>
       </c>
       <c r="L7" s="8"/>
-      <c r="M7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="8">
-        <v>1</v>
-      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
       <c r="O7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="P7" s="8">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>9</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>6</v>
+        <v>25</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="9"/>
+      <c r="T7" s="16" t="s">
+        <v>100</v>
       </c>
       <c r="V7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W7" t="s">
         <v>20</v>
@@ -1077,7 +1084,7 @@
         <v>25</v>
       </c>
       <c r="W8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s">
         <v>12</v>
@@ -1138,9 +1145,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1164,15 +1171,9 @@
         <v>23</v>
       </c>
       <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>10</v>
-      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
@@ -1193,13 +1194,13 @@
         <v>48</v>
       </c>
       <c r="V11" t="s">
+        <v>75</v>
+      </c>
+      <c r="W11" t="s">
         <v>76</v>
       </c>
-      <c r="W11" t="s">
-        <v>77</v>
-      </c>
       <c r="X11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1255,13 +1256,13 @@
         <v>72</v>
       </c>
       <c r="X12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -1322,7 +1323,7 @@
         <v>52</v>
       </c>
       <c r="X14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1390,7 +1391,7 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -1445,10 +1446,10 @@
         <v>51</v>
       </c>
       <c r="W17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1509,7 +1510,7 @@
     <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1570,7 +1571,7 @@
         <v>47</v>
       </c>
       <c r="Z20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1622,16 +1623,16 @@
         <v>10</v>
       </c>
       <c r="V21" t="s">
+        <v>85</v>
+      </c>
+      <c r="W21" t="s">
         <v>86</v>
-      </c>
-      <c r="W21" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1684,10 +1685,10 @@
         <v>46</v>
       </c>
       <c r="W23" t="s">
+        <v>87</v>
+      </c>
+      <c r="X23" s="16" t="s">
         <v>88</v>
-      </c>
-      <c r="X23" s="16" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1739,15 +1740,15 @@
     </row>
     <row r="25" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>95</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -1864,7 +1865,7 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -1999,7 +2000,7 @@
       </c>
       <c r="R32" s="9"/>
       <c r="V32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2083,6 +2084,14 @@
       </c>
       <c r="W37" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V38" t="s">
+        <v>98</v>
+      </c>
+      <c r="W38" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B907F61-34F1-417E-88C6-66164D9D94AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB88969-CBB2-413B-9D1D-855F5664ED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
@@ -327,16 +327,16 @@
     <t>минус_ прерывает процесс</t>
   </si>
   <si>
-    <t>настройки 0</t>
-  </si>
-  <si>
     <t>XX</t>
   </si>
   <si>
     <t>RCP 11</t>
   </si>
   <si>
-    <t>влево вправо перемещение курсора, интер выбор и потом вверх вниз увеличить или уменьшить, ентер ввод вверх назад (выйти из энтера, курсор на 0)</t>
+    <t>основной экран 0</t>
+  </si>
+  <si>
+    <t>влево вправо перемещение курсора, интер выбор и потом плюс минус увеличить или уменьшить, ентер ввод вверх назад (выйти из энтера, курсор на 0)</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="38" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V38" t="s">
+        <v>97</v>
+      </c>
+      <c r="W38" t="s">
         <v>98</v>
-      </c>
-      <c r="W38" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB88969-CBB2-413B-9D1D-855F5664ED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0751DBA1-AD14-40E3-BD2E-2FB284684E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
+    <workbookView xWindow="29580" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="103">
   <si>
     <t>a</t>
   </si>
@@ -123,12 +123,6 @@
     <t>_</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>&gt;</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>M1_P</t>
   </si>
   <si>
-    <t>M1 pulses per rpm</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
@@ -183,9 +174,6 @@
     <t>индикация</t>
   </si>
   <si>
-    <t>туда сюда</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -288,18 +276,12 @@
     <t>Step, Dir, En inverse инверсия выходных сигналов</t>
   </si>
   <si>
-    <t>40*88(88 это число импульсов на обород моего двигателя)</t>
-  </si>
-  <si>
     <t xml:space="preserve">test </t>
   </si>
   <si>
     <t>провернет на оборот (указанное число импульсов) для m2 не критично всеравно по концевикам работает ставим 1000</t>
   </si>
   <si>
-    <t>max speed в импульсах в 0.1 секунд</t>
-  </si>
-  <si>
     <t>тут тестирование может сделаю в будущем, так-то просто вобьем константу, эта скорость будет максимальной, например надо будет найти максимальную скорость от числа импульсов так чтобы шаги не пропускались (если шд) это и будет 100% на галвном экране</t>
   </si>
   <si>
@@ -337,6 +319,30 @@
   </si>
   <si>
     <t>влево вправо перемещение курсора, интер выбор и потом плюс минус увеличить или уменьшить, ентер ввод вверх назад (выйти из энтера, курсор на 0)</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>P:</t>
+  </si>
+  <si>
+    <t>Глубина резания в мм</t>
+  </si>
+  <si>
+    <t>Imm</t>
+  </si>
+  <si>
+    <t>импульсов на миллиметр</t>
+  </si>
+  <si>
+    <t>max speed в импульсах в секунду в нашем случае это 50 для обоих</t>
+  </si>
+  <si>
+    <t>40*88(88 это число импульсов на оборот моего двигателя)</t>
+  </si>
+  <si>
+    <t>для M2 это импульсов на миллиметр(далее умножается на уставку), для M1 это импульсов на оборот (на полный оборот удг, это значение далее делится на число зубов)</t>
   </si>
 </sst>
 </file>
@@ -968,6 +974,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>96</v>
+      </c>
+      <c r="W6" t="s">
+        <v>97</v>
+      </c>
       <c r="X6" t="s">
         <v>9</v>
       </c>
@@ -977,7 +989,7 @@
     </row>
     <row r="7" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1004,27 +1016,31 @@
         <v>10</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="8">
+        <v>2</v>
+      </c>
       <c r="O7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="P7" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>9</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>6</v>
+      </c>
       <c r="T7" s="16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="V7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="W7" t="s">
         <v>20</v>
@@ -1039,52 +1055,54 @@
     <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
       <c r="C8" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="11">
+        <v>26</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1</v>
+      </c>
+      <c r="G8" s="11">
         <v>2</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="11">
-        <v>9</v>
-      </c>
-      <c r="G8" s="11">
-        <v>9</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="11">
-        <v>2</v>
-      </c>
+      <c r="H8" s="11">
+        <v>3</v>
+      </c>
+      <c r="I8" s="11">
+        <v>4</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="P8" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>9</v>
-      </c>
       <c r="R8" s="12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V8" t="s">
         <v>25</v>
       </c>
       <c r="W8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Z8" t="s">
         <v>12</v>
@@ -1147,16 +1165,16 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>26</v>
@@ -1171,9 +1189,15 @@
         <v>23</v>
       </c>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
+      <c r="J11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
@@ -1191,25 +1215,25 @@
         <v>23</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="V11" t="s">
+        <v>71</v>
+      </c>
+      <c r="W11" t="s">
+        <v>72</v>
+      </c>
+      <c r="X11" t="s">
         <v>75</v>
-      </c>
-      <c r="W11" t="s">
-        <v>76</v>
-      </c>
-      <c r="X11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>26</v>
@@ -1225,10 +1249,10 @@
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L12" s="11">
         <v>1</v>
@@ -1250,19 +1274,26 @@
         <v>23</v>
       </c>
       <c r="V12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="W12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="X12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>98</v>
+      </c>
+      <c r="W13" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -1289,41 +1320,23 @@
         <v>1</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="8">
-        <v>1</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" s="9">
-        <v>2</v>
-      </c>
-      <c r="S14" s="13" t="s">
-        <v>49</v>
-      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="13"/>
       <c r="V14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="W14" s="16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="X14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1351,7 +1364,7 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L15" s="11">
         <v>1</v>
@@ -1363,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P15" s="11">
         <v>2</v>
@@ -1375,23 +1388,23 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W16" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -1406,7 +1419,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8" t="s">
@@ -1416,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>3</v>
@@ -1425,7 +1438,7 @@
         <v>8</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>2</v>
@@ -1443,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="W17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1464,7 +1477,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
@@ -1474,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>3</v>
@@ -1483,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>2</v>
@@ -1501,16 +1514,16 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1550,7 +1563,7 @@
       </c>
       <c r="N20" s="8"/>
       <c r="O20" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>4</v>
@@ -1562,16 +1575,16 @@
         <v>10</v>
       </c>
       <c r="V20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="W20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="X20" s="16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Z20" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1611,7 +1624,7 @@
       </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>4</v>
@@ -1623,16 +1636,16 @@
         <v>10</v>
       </c>
       <c r="V21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1670,7 +1683,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>4</v>
@@ -1682,13 +1695,13 @@
         <v>10</v>
       </c>
       <c r="V23" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="W23" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="X23" s="16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1726,7 +1739,7 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>4</v>
@@ -1740,15 +1753,15 @@
     </row>
     <row r="25" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -1773,7 +1786,7 @@
         <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>27</v>
@@ -1865,7 +1878,7 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -1880,19 +1893,19 @@
         <v>24</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>21</v>
@@ -1915,10 +1928,10 @@
       <c r="A30" s="17"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>0</v>
@@ -1931,13 +1944,13 @@
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>24</v>
@@ -1946,7 +1959,7 @@
         <v>8</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
@@ -1955,7 +1968,7 @@
     <row r="31" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>25</v>
@@ -1978,10 +1991,10 @@
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>8</v>
@@ -2000,7 +2013,7 @@
       </c>
       <c r="R32" s="9"/>
       <c r="V32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2015,7 +2028,7 @@
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G33" s="11">
         <v>1</v>
@@ -2028,7 +2041,7 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L33" s="11">
         <v>2</v>
@@ -2048,50 +2061,50 @@
         <v>22</v>
       </c>
       <c r="V33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="W33" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V34" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="W34" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V35" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W35" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V36" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="W36" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V37" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="W37" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="2:23" x14ac:dyDescent="0.25">
       <c r="V38" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="W38" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0751DBA1-AD14-40E3-BD2E-2FB284684E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205CFF6F-C9A6-47F0-9E2D-AB6A072950AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="104">
   <si>
     <t>a</t>
   </si>
@@ -63,9 +63,6 @@
     <t>r</t>
   </si>
   <si>
-    <t>360-импульсов на оборот</t>
-  </si>
-  <si>
     <t>t</t>
   </si>
   <si>
@@ -81,21 +78,12 @@
     <t>s</t>
   </si>
   <si>
-    <t>360/(tooth-1)</t>
-  </si>
-  <si>
-    <t>выборка люфта провернуть на первый зуб в холостую</t>
-  </si>
-  <si>
     <t>v</t>
   </si>
   <si>
     <t>вверх вниз перемещают курсор (с переходом на второй экран)</t>
   </si>
   <si>
-    <t>zadanie</t>
-  </si>
-  <si>
     <t>2-255</t>
   </si>
   <si>
@@ -168,9 +156,6 @@
     <t>m1_M</t>
   </si>
   <si>
-    <t>импульсов на оборот, для удг формула =передаточноеУДГ*передаточноеМ*числоимп_энк  далее делим на число зубов</t>
-  </si>
-  <si>
     <t>индикация</t>
   </si>
   <si>
@@ -339,10 +324,29 @@
     <t>max speed в импульсах в секунду в нашем случае это 50 для обоих</t>
   </si>
   <si>
-    <t>40*88(88 это число импульсов на оборот моего двигателя)</t>
-  </si>
-  <si>
     <t>для M2 это импульсов на миллиметр(далее умножается на уставку), для M1 это импульсов на оборот (на полный оборот удг, это значение далее делится на число зубов)</t>
+  </si>
+  <si>
+    <t>360/(tooth-1) 360-импульсов на оборот выборка люфта провернуть на первый зуб в холостую</t>
+  </si>
+  <si>
+    <t>управление</t>
+  </si>
+  <si>
+    <t>параметр</t>
+  </si>
+  <si>
+    <t>описание</t>
+  </si>
+  <si>
+    <t>значение</t>
+  </si>
+  <si>
+    <t>+- ввод</t>
+  </si>
+  <si>
+    <t>импульсов на оборот, для удг формула =передаточноеУДГ*передаточноеМ*числоимп_энк  далее делим на число зубов
+40*88(88 это число импульсов на оборот моего двигателя)</t>
   </si>
 </sst>
 </file>
@@ -560,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -582,6 +586,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE51753-6362-42E1-858B-3262C08793D0}">
-  <dimension ref="A4:Z38"/>
+  <dimension ref="A5:W45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -909,21 +916,13 @@
     <col min="16" max="16" width="3.7109375" customWidth="1"/>
     <col min="17" max="17" width="3.28515625" customWidth="1"/>
     <col min="18" max="18" width="3.140625" customWidth="1"/>
-    <col min="20" max="20" width="53.5703125" customWidth="1"/>
-    <col min="23" max="23" width="59.28515625" customWidth="1"/>
-    <col min="24" max="24" width="68.28515625" customWidth="1"/>
-    <col min="26" max="26" width="60.28515625" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" customWidth="1"/>
+    <col min="21" max="21" width="59.28515625" style="16" customWidth="1"/>
+    <col min="22" max="22" width="68.28515625" style="16" customWidth="1"/>
+    <col min="23" max="23" width="60.28515625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="V4" t="s">
-        <v>19</v>
-      </c>
-      <c r="W4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>0</v>
       </c>
@@ -972,33 +971,42 @@
       <c r="R5">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V6" t="s">
-        <v>96</v>
-      </c>
-      <c r="W6" t="s">
-        <v>97</v>
-      </c>
-      <c r="X6" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="45" x14ac:dyDescent="0.25">
+      <c r="T5" t="s">
+        <v>99</v>
+      </c>
+      <c r="U5" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>5</v>
@@ -1013,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -1036,32 +1044,29 @@
       <c r="R7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V7" t="s">
-        <v>74</v>
-      </c>
-      <c r="W7" t="s">
-        <v>20</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="T7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="V7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="W7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Z7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
       <c r="C8" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F8" s="11">
         <v>1</v>
@@ -1076,18 +1081,18 @@
         <v>4</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P8" s="11" t="s">
         <v>0</v>
@@ -1096,24 +1101,24 @@
         <v>8</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="V8" t="s">
-        <v>25</v>
-      </c>
-      <c r="W8" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W9" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>0</v>
       </c>
@@ -1163,21 +1168,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F11" s="8">
         <v>1</v>
@@ -1186,24 +1191,24 @@
         <v>5</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>4</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P11" s="8">
         <v>1</v>
@@ -1212,31 +1217,31 @@
         <v>5</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="V11" t="s">
-        <v>71</v>
-      </c>
-      <c r="W11" t="s">
-        <v>72</v>
-      </c>
-      <c r="X11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="T11" t="s">
+        <v>66</v>
+      </c>
+      <c r="U11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="V11" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="C12" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F12" s="11">
         <v>2</v>
@@ -1245,24 +1250,24 @@
         <v>5</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L12" s="11">
         <v>1</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P12" s="11">
         <v>2</v>
@@ -1271,44 +1276,44 @@
         <v>5</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="V12" t="s">
-        <v>67</v>
-      </c>
-      <c r="W12" t="s">
-        <v>68</v>
-      </c>
-      <c r="X12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V13" t="s">
-        <v>98</v>
-      </c>
-      <c r="W13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s">
+        <v>62</v>
+      </c>
+      <c r="U12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="V12" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T13" t="s">
+        <v>93</v>
+      </c>
+      <c r="U13" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E14" s="8">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>3</v>
@@ -1329,29 +1334,29 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="9"/>
       <c r="S14" s="13"/>
-      <c r="V14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W14" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="X14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="V14" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
       <c r="C15" s="10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E15" s="11">
         <v>2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>3</v>
@@ -1364,7 +1369,7 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L15" s="11">
         <v>1</v>
@@ -1376,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="P15" s="11">
         <v>2</v>
@@ -1387,24 +1392,24 @@
       <c r="R15" s="11">
         <v>1</v>
       </c>
-      <c r="V15" t="s">
-        <v>41</v>
-      </c>
-      <c r="W15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V16" t="s">
-        <v>35</v>
-      </c>
-      <c r="W16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T15" t="s">
+        <v>37</v>
+      </c>
+      <c r="U15" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T16" t="s">
+        <v>33</v>
+      </c>
+      <c r="U16" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -1419,17 +1424,17 @@
         <v>5</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>3</v>
@@ -1438,7 +1443,7 @@
         <v>8</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>2</v>
@@ -1455,17 +1460,17 @@
       <c r="R17" s="9">
         <v>1</v>
       </c>
-      <c r="V17" t="s">
-        <v>47</v>
-      </c>
-      <c r="W17" t="s">
-        <v>79</v>
-      </c>
-      <c r="X17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T17" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="V17" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
       <c r="C18" s="10" t="s">
         <v>7</v>
@@ -1477,17 +1482,17 @@
         <v>5</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>3</v>
@@ -1496,7 +1501,7 @@
         <v>8</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>2</v>
@@ -1513,17 +1518,17 @@
       <c r="R18" s="12">
         <v>1</v>
       </c>
-      <c r="V18" t="s">
-        <v>33</v>
-      </c>
-      <c r="W18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:26" ht="45" x14ac:dyDescent="0.25">
+      <c r="T18" t="s">
+        <v>29</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1535,59 +1540,56 @@
         <v>1</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N20" s="8"/>
       <c r="O20" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="V20" t="s">
-        <v>37</v>
-      </c>
-      <c r="W20" t="s">
-        <v>38</v>
-      </c>
-      <c r="X20" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="T20" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="C21" s="10" t="s">
         <v>7</v>
@@ -1596,56 +1598,56 @@
         <v>2</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P21" s="11" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="V21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" t="s">
+        <v>75</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="W21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:26" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1657,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>7</v>
@@ -1666,45 +1668,45 @@
         <v>5</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="V23" t="s">
-        <v>43</v>
-      </c>
-      <c r="W23" t="s">
-        <v>100</v>
-      </c>
-      <c r="X23" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="T23" t="s">
+        <v>39</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="V23" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="C24" s="10" t="s">
         <v>7</v>
@@ -1713,7 +1715,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>7</v>
@@ -1722,58 +1724,58 @@
         <v>5</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>4</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>4</v>
@@ -1783,31 +1785,31 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
@@ -1826,7 +1828,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="6"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>0</v>
       </c>
@@ -1876,105 +1878,105 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B29">
         <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="6"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>5</v>
@@ -1991,10 +1993,10 @@
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>8</v>
@@ -2003,20 +2005,26 @@
         <v>5</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R32" s="9"/>
-      <c r="V32" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T32" t="s">
+        <v>51</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="W32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <v>8</v>
       </c>
@@ -2024,11 +2032,11 @@
         <v>7</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G33" s="11">
         <v>1</v>
@@ -2041,7 +2049,7 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L33" s="11">
         <v>2</v>
@@ -2055,60 +2063,78 @@
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R33" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="V33" t="s">
+        <v>18</v>
+      </c>
+      <c r="T33" t="s">
+        <v>53</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T34" t="s">
+        <v>55</v>
+      </c>
+      <c r="U34" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="W33" t="s">
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T35" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V34" t="s">
+      <c r="U35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="W34" t="s">
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T36" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V35" t="s">
+      <c r="U36" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="W35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V36" t="s">
-        <v>62</v>
-      </c>
-      <c r="W36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V37" t="s">
-        <v>64</v>
-      </c>
-      <c r="W37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V38" t="s">
-        <v>91</v>
-      </c>
-      <c r="W38" t="s">
-        <v>92</v>
-      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T37" t="s">
+        <v>86</v>
+      </c>
+      <c r="U37" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U40"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T41" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="U41" s="17"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="T41:U45"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A7:A8"/>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205CFF6F-C9A6-47F0-9E2D-AB6A072950AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC0B65-9AFC-4DE5-9926-6D8C08FED3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="106">
   <si>
     <t>a</t>
   </si>
@@ -347,6 +347,12 @@
   <si>
     <t>импульсов на оборот, для удг формула =передаточноеУДГ*передаточноеМ*числоимп_энк  далее делим на число зубов
 40*88(88 это число импульсов на оборот моего двигателя)</t>
+  </si>
+  <si>
+    <t>Del:XXXX</t>
+  </si>
+  <si>
+    <t>Задержка между переключениями M1 M2 после RCP или доставки задания</t>
   </si>
 </sst>
 </file>
@@ -584,11 +590,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -991,12 +997,12 @@
       <c r="U6" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="W6" s="18" t="s">
+      <c r="W6" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>64</v>
       </c>
       <c r="B7">
@@ -1058,7 +1064,7 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
       <c r="C8" s="10" t="s">
         <v>22</v>
       </c>
@@ -1169,7 +1175,7 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B11">
@@ -1233,7 +1239,7 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
+      <c r="A12" s="18"/>
       <c r="C12" s="10" t="s">
         <v>25</v>
       </c>
@@ -1297,7 +1303,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>65</v>
       </c>
       <c r="B14">
@@ -1325,14 +1331,30 @@
         <v>1</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="9"/>
+      <c r="K14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="S14" s="13"/>
       <c r="T14" t="s">
         <v>36</v>
@@ -1345,7 +1367,7 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="C15" s="10" t="s">
         <v>21</v>
       </c>
@@ -1399,16 +1421,16 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="T16" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B17">
@@ -1471,7 +1493,7 @@
       </c>
     </row>
     <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
       <c r="C18" s="10" t="s">
         <v>7</v>
       </c>
@@ -1525,9 +1547,16 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T19" t="s">
+        <v>33</v>
+      </c>
+      <c r="U19" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="20" spans="1:23" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>79</v>
       </c>
       <c r="B20">
@@ -1590,7 +1619,7 @@
       </c>
     </row>
     <row r="21" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
+      <c r="A21" s="18"/>
       <c r="C21" s="10" t="s">
         <v>7</v>
       </c>
@@ -1646,7 +1675,7 @@
     </row>
     <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:23" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>80</v>
       </c>
       <c r="B23">
@@ -1707,7 +1736,7 @@
       </c>
     </row>
     <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
       <c r="C24" s="10" t="s">
         <v>7</v>
       </c>
@@ -1762,7 +1791,7 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>81</v>
       </c>
       <c r="B26">
@@ -1810,7 +1839,7 @@
       <c r="R26" s="3"/>
     </row>
     <row r="27" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
+      <c r="A27" s="18"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -1879,7 +1908,7 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B29">
@@ -1927,7 +1956,7 @@
       <c r="R29" s="3"/>
     </row>
     <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
+      <c r="A30" s="18"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
         <v>35</v>
@@ -2111,26 +2140,26 @@
       <c r="U40"/>
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="T41" s="17" t="s">
+      <c r="T41" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="U41" s="17"/>
+      <c r="U41" s="18"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC0B65-9AFC-4DE5-9926-6D8C08FED3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4435645F-8FF3-4878-9F68-342ED19D5D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>

--- a/screen.xlsx
+++ b/screen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\CNC_dividing_head\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\CNC_dividing_head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4435645F-8FF3-4878-9F68-342ED19D5D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655E3C43-639A-42F4-8F6C-7CD26CD646E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81485BE0-4FC2-4F8C-A7B1-B0057AD691FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="107">
   <si>
     <t>a</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Задержка между переключениями M1 M2 после RCP или доставки задания</t>
+  </si>
+  <si>
+    <t>не используем есть же инверсия пина DIR</t>
   </si>
 </sst>
 </file>
@@ -1554,6 +1557,9 @@
       <c r="U19" s="16" t="s">
         <v>34</v>
       </c>
+      <c r="V19" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="20" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
